--- a/sheets/민요/검수/울산 아가씨.xlsx
+++ b/sheets/민요/검수/울산 아가씨.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,48 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4791,8 +4913,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:U14"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -4815,1044 +4941,1047 @@
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">울산 아가씨 — 민요채보-3/울산 아가씨.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="T2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="U2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">울산 아가씨</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+      <c s="8" r="R2"/>
+      <c s="8" r="S2"/>
+      <c s="8" r="T2"/>
+      <c s="8" r="U2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">좋기도</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">동해라</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">실백자</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 姑</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="Q3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">큰애기</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="R3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="S3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">경치도</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="T3" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="U3" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">동해나</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C4" s="17"/>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E4" s="17"/>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="I4" s="18"/>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢</t>
-        </is>
-      </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="K4" s="17"/>
+      <c r="L4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="M4" s="17"/>
+      <c r="N4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="O4" s="17"/>
+      <c r="P4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 仲</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="Q4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">마음은</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="R4" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="S4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="T4" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="U4" s="3"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="U4" s="18"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C5" s="19"/>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E5" s="19"/>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G5" s="19"/>
+      <c r="H5" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢</t>
-        </is>
-      </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I5" s="19"/>
+      <c r="J5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="K5" s="19"/>
+      <c r="L5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="M5" s="19"/>
+      <c r="N5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="O5" s="19"/>
+      <c r="P5" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="S5" s="19"/>
+      <c r="T5" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢</t>
-        </is>
-      </c>
-      <c r="U5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="U5" s="19"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="C6" s="20"/>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E6" s="16"/>
+      <c r="F6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G6" s="20"/>
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">을산은</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 㳞</t>
         </is>
       </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="K6" s="20"/>
+      <c r="L6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">헤에</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="O6" s="16"/>
+      <c r="P6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="Q6" s="16"/>
+      <c r="R6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr">
+      <c r="S6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">지만</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="T6" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="U6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">울산은</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C7" s="17"/>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E7" s="17"/>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G7" s="17"/>
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="I7" s="17"/>
+      <c r="J7" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K7" s="17"/>
+      <c r="L7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="M7" s="17"/>
+      <c r="N7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="O7" s="17"/>
+      <c r="P7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="Q7" s="17"/>
+      <c r="R7" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="U7" s="2"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="S7" s="17"/>
+      <c r="T7" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U7" s="17"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C8" s="19"/>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E8" s="19"/>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G8" s="19"/>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢</t>
-        </is>
-      </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I8" s="19"/>
+      <c r="J8" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K8" s="19"/>
+      <c r="L8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="M8" s="19"/>
+      <c r="N8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="O8" s="19"/>
+      <c r="P8" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2" t="inlineStr">
+      <c r="S8" s="19"/>
+      <c r="T8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="U8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="U8" s="19"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E9" s="16"/>
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G9" s="16"/>
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="I9" s="16"/>
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="M9" s="16"/>
+      <c r="N9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">좋기도</t>
         </is>
       </c>
-      <c r="P9" s="3" t="inlineStr">
+      <c r="P9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="Q9" s="3" t="inlineStr">
+      <c r="Q9" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">인심도</t>
         </is>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="R9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2" t="inlineStr">
+      <c r="S9" s="16"/>
+      <c r="T9" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 潢</t>
         </is>
       </c>
-      <c r="U9" s="2" t="inlineStr">
+      <c r="U9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">잣나무그</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C10" s="17"/>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E10" s="17"/>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G10" s="17"/>
+      <c r="H10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="I10" s="17"/>
+      <c r="J10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="K10" s="17"/>
+      <c r="L10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="M10" s="17"/>
+      <c r="N10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="O10" s="2"/>
-      <c r="P10" s="3" t="inlineStr">
+      <c r="O10" s="17"/>
+      <c r="P10" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="Q10" s="18"/>
+      <c r="R10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2" t="inlineStr">
+      <c r="S10" s="17"/>
+      <c r="T10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="U10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="U10" s="17"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C11" s="19"/>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E11" s="19"/>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G11" s="19"/>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I11" s="19"/>
+      <c r="J11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="K11" s="19"/>
+      <c r="L11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="M11" s="19"/>
+      <c r="N11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 姑</t>
         </is>
       </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="O11" s="19"/>
+      <c r="P11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="Q11" s="19"/>
+      <c r="R11" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="S11" s="19"/>
+      <c r="T11" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="U11" s="2"/>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="U11" s="19"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E12" s="16"/>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G12" s="16"/>
+      <c r="H12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="I12" s="16"/>
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="K12" s="16"/>
+      <c r="L12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="M12" s="16"/>
+      <c r="N12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="O12" s="16"/>
+      <c r="P12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 姑</t>
         </is>
       </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="Q12" s="16"/>
+      <c r="R12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2" t="inlineStr">
+      <c r="S12" s="16"/>
+      <c r="T12" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="U12" s="2" t="inlineStr">
+      <c r="U12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">늘</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C13" s="17"/>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E13" s="17"/>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G13" s="17"/>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I13" s="17"/>
+      <c r="J13" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K13" s="17"/>
+      <c r="L13" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M13" s="17"/>
+      <c r="N13" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="O13" s="17"/>
+      <c r="P13" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="Q13" s="17"/>
+      <c r="R13" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="S13" s="17"/>
+      <c r="T13" s="14" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 姑</t>
-        </is>
-      </c>
-      <c r="U13" s="2"/>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="U13" s="17"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="C14" s="19"/>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="E14" s="19"/>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="G14" s="19"/>
+      <c r="H14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2" t="inlineStr">
+      <c r="I14" s="19"/>
+      <c r="J14" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="K14" s="19"/>
+      <c r="L14" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="M14" s="19"/>
+      <c r="N14" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="O14" s="19"/>
+      <c r="P14" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="Q14" s="19"/>
+      <c r="R14" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">·</t>
+        </is>
+      </c>
+      <c r="S14" s="19"/>
+      <c r="T14" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
 姑</t>
         </is>
       </c>
-      <c r="U14" s="2"/>
+      <c r="U14" s="19"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:U2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="61"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/울산 아가씨.xlsx
+++ b/sheets/민요/검수/울산 아가씨.xlsx
@@ -413,7 +413,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -632,12 +632,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -869,13 +869,13 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―姑</t>
+          <t xml:space="preserve">無|–姑</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―姑</t>
+–姑</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―姑</t>
+          <t xml:space="preserve">–姑</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―姑</t>
+          <t xml:space="preserve">–姑</t>
         </is>
       </c>
       <c r="I12" s="2"/>
@@ -1061,13 +1061,13 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―仲</t>
+          <t xml:space="preserve">姑|–仲</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―仲</t>
+–仲</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1183,13 +1183,13 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―姑</t>
+          <t xml:space="preserve">無|–姑</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―姑</t>
+–姑</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1301,13 +1301,13 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―潢</t>
+          <t xml:space="preserve">無|–潢</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -1341,13 +1341,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―姑</t>
+          <t xml:space="preserve">無|–姑</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―姑</t>
+–姑</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1612,13 +1612,13 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―㳞</t>
+          <t xml:space="preserve">潢|–㳞</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―㳞</t>
+–㳞</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -1652,13 +1652,13 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|―㳞</t>
+          <t xml:space="preserve">㳞|–㳞</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―㳞</t>
+–㳞</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|△</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -1768,13 +1768,13 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―潢</t>
+          <t xml:space="preserve">潢|–潢</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -1808,13 +1808,13 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―無</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -1888,13 +1888,13 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―姑</t>
+          <t xml:space="preserve">–|–姑</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―姑</t>
+          <t xml:space="preserve">–
+–姑</t>
         </is>
       </c>
       <c r="I36" s="2"/>
@@ -1998,13 +1998,13 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―潢</t>
+          <t xml:space="preserve">無|–潢</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2038,13 +2038,13 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―無</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2156,13 +2156,13 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―姑</t>
+          <t xml:space="preserve">無|–姑</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―姑</t>
+–姑</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2235,13 +2235,13 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―姑</t>
+          <t xml:space="preserve">無|–姑</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―姑</t>
+–姑</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲潢</t>
+          <t xml:space="preserve">–|仲潢</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲潢</t>
         </is>
       </c>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I60" s="2"/>
@@ -2947,12 +2947,12 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―㳞</t>
+          <t xml:space="preserve">–㳞</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―㳞</t>
+          <t xml:space="preserve">–㳞</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3025,13 +3025,13 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―潢</t>
+          <t xml:space="preserve">無|–潢</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3065,13 +3065,13 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―無</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3144,13 +3144,13 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―姑</t>
+          <t xml:space="preserve">無|–姑</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―姑</t>
+–姑</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -3184,13 +3184,13 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃|―姑</t>
+          <t xml:space="preserve">黃|–姑</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
-―姑</t>
+–姑</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I72" s="2"/>
@@ -3443,7 +3443,7 @@
       <c r="F4" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="G4" s="9" t="inlineStr">
@@ -3465,7 +3465,7 @@
       <c r="J4" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―仲</t>
+–仲</t>
         </is>
       </c>
       <c r="K4" s="12" t="inlineStr">
@@ -3489,7 +3489,7 @@
       <c r="A5" s="0"/>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―㳞</t>
+          <t xml:space="preserve">–㳞</t>
         </is>
       </c>
       <c r="C5" s="10" t="inlineStr">
@@ -3506,7 +3506,7 @@
       <c r="F5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="10" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K5" s="10" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="L5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M5" s="10" t="inlineStr">
@@ -3580,7 +3580,7 @@
       <c r="H6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―㳞</t>
+–㳞</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
@@ -3614,7 +3614,7 @@
       <c r="B7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲潢</t>
         </is>
       </c>
@@ -3642,7 +3642,7 @@
       <c r="H7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
-―㳞</t>
+–㳞</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -3653,7 +3653,7 @@
       <c r="J7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―姑</t>
+–姑</t>
         </is>
       </c>
       <c r="K7" s="9" t="inlineStr">
@@ -3678,7 +3678,7 @@
       <c r="B8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -3700,7 +3700,7 @@
       <c r="F8" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―姑</t>
+–姑</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -3806,7 +3806,7 @@
       <c r="B10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―姑</t>
+–姑</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -3823,7 +3823,7 @@
       <c r="F10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―姑</t>
+–姑</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr">
@@ -3834,7 +3834,7 @@
       <c r="H10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
@@ -3845,7 +3845,7 @@
       <c r="J10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -3870,7 +3870,7 @@
       <c r="B11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
-―姑</t>
+–姑</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -3897,7 +3897,7 @@
       <c r="H11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="I11" s="10" t="inlineStr">
@@ -3908,7 +3908,7 @@
       <c r="J11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―姑</t>
+–姑</t>
         </is>
       </c>
       <c r="K11" s="10" t="inlineStr">
@@ -3919,7 +3919,7 @@
       <c r="L11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―姑</t>
+–姑</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr">
@@ -3992,13 +3992,13 @@
       <c r="A13" s="0"/>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E13" s="9"/>
@@ -4010,8 +4010,8 @@
       <c r="G13" s="9"/>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―姑</t>
+          <t xml:space="preserve">–
+–姑</t>
         </is>
       </c>
       <c r="I13" s="9"/>
@@ -4023,7 +4023,7 @@
       <c r="K13" s="9"/>
       <c r="L13" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―姑</t>
+          <t xml:space="preserve">–姑</t>
         </is>
       </c>
       <c r="M13" s="9"/>

--- a/sheets/민요/검수/울산 아가씨.xlsx
+++ b/sheets/민요/검수/울산 아가씨.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3342,81 +3380,81 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">울산 아가씨</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">실</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">큰</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">경</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
@@ -3424,62 +3462,62 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">해</t>
         </is>
       </c>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="E4" s="23"/>
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –潢</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr">
+      <c r="G4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">뻑</t>
         </is>
       </c>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">애</t>
         </is>
       </c>
-      <c r="J4" s="18" t="inlineStr">
+      <c r="J4" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –仲</t>
         </is>
       </c>
-      <c r="K4" s="12" t="inlineStr">
+      <c r="K4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">치</t>
         </is>
       </c>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">해</t>
         </is>
@@ -3487,59 +3525,59 @@
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–㳞</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="26"/>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –無</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="K5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="10" t="inlineStr">
+      <c r="M5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -3547,63 +3585,63 @@
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢姑</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">없</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –㳞</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">마</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
       </c>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="M6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
@@ -3611,63 +3649,63 @@
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –潢</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲潢</t>
         </is>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="23"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 –㳞</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">음은</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –姑</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 潢</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
@@ -3675,63 +3713,63 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –無</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –姑</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="I8" s="26"/>
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="K8" s="10" t="inlineStr">
+      <c r="K8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="M8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
@@ -3739,63 +3777,63 @@
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">전</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">인</t>
         </is>
       </c>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">인</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="M9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">잣</t>
         </is>
@@ -3803,63 +3841,63 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –姑</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">기도</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="23"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –姑</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">북쌈</t>
         </is>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –潢</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">심도</t>
         </is>
       </c>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="J10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –潢</t>
         </is>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="K10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">심도</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 黃</t>
         </is>
       </c>
-      <c r="M10" s="9" t="inlineStr">
+      <c r="M10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">나무</t>
         </is>
@@ -3867,62 +3905,62 @@
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 –姑</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="26"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
         </is>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –無</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="I11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">좋구</t>
         </is>
       </c>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="J11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –姑</t>
         </is>
       </c>
-      <c r="K11" s="10" t="inlineStr">
+      <c r="K11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">좋구</t>
         </is>
       </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –姑</t>
         </is>
       </c>
-      <c r="M11" s="10" t="inlineStr">
+      <c r="M11" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">그</t>
         </is>
@@ -3930,59 +3968,59 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="22"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
       </c>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
       </c>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="L12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M12" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">늘</t>
         </is>
@@ -3990,82 +4028,82 @@
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="23"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="23"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="G13" s="23"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –姑</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="I13" s="23"/>
+      <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="K13" s="23"/>
+      <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–姑</t>
         </is>
       </c>
-      <c r="M13" s="9"/>
+      <c r="M13" s="23"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="C14" s="27"/>
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="E14" s="27"/>
+      <c r="F14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="27"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="18" t="inlineStr">
+      <c r="I14" s="26"/>
+      <c r="J14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K14" s="13"/>
-      <c r="L14" s="18" t="inlineStr">
+      <c r="K14" s="27"/>
+      <c r="L14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="M14" s="13"/>
+      <c r="M14" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/울산 아가씨.xlsx
+++ b/sheets/민요/검수/울산 아가씨.xlsx
@@ -3361,24 +3361,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E4" s="23"/>
@@ -3523,7 +3523,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E5" s="26"/>
@@ -3583,7 +3583,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E10" s="23"/>
@@ -3903,7 +3903,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E11" s="26"/>
@@ -3966,7 +3966,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
       </c>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E12" s="22"/>
@@ -4026,7 +4026,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
       <c r="E13" s="23"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G13" s="23"/>
@@ -4055,7 +4055,7 @@
       <c r="I13" s="23"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K13" s="23"/>
@@ -4066,23 +4066,23 @@
       </c>
       <c r="M13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C14" s="27"/>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E14" s="27"/>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G14" s="27"/>
@@ -4094,7 +4094,7 @@
       <c r="I14" s="26"/>
       <c r="J14" s="24" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K14" s="27"/>

--- a/sheets/민요/검수/울산 아가씨.xlsx
+++ b/sheets/민요/검수/울산 아가씨.xlsx
@@ -3685,7 +3685,8 @@
       </c>
       <c r="I7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">음은</t>
+          <t xml:space="preserve">음
+은</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -3849,7 +3850,8 @@
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">기도</t>
+          <t xml:space="preserve">기
+도</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -3866,7 +3868,8 @@
       </c>
       <c r="G10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">북쌈</t>
+          <t xml:space="preserve">북
+쌈</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -3877,7 +3880,8 @@
       </c>
       <c r="I10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">심도</t>
+          <t xml:space="preserve">심
+도</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
@@ -3888,7 +3892,8 @@
       </c>
       <c r="K10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">심도</t>
+          <t xml:space="preserve">심
+도</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -3899,7 +3904,8 @@
       </c>
       <c r="M10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">나무</t>
+          <t xml:space="preserve">나
+무</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3946,8 @@
       </c>
       <c r="I11" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">좋구</t>
+          <t xml:space="preserve">좋
+구</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -3951,7 +3958,8 @@
       </c>
       <c r="K11" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">좋구</t>
+          <t xml:space="preserve">좋
+구</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">

--- a/sheets/민요/검수/울산 아가씨.xlsx
+++ b/sheets/민요/검수/울산 아가씨.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -233,6 +238,21 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3404,7 +3424,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
@@ -3414,7 +3434,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -3424,7 +3444,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">실</t>
         </is>
@@ -3434,7 +3454,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">큰</t>
         </is>
@@ -3444,7 +3464,7 @@
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">경</t>
         </is>
@@ -3454,7 +3474,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M3" s="22" t="inlineStr">
+      <c r="M3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
@@ -3467,7 +3487,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">해</t>
         </is>
@@ -3477,14 +3497,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="29"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –潢</t>
         </is>
       </c>
-      <c r="G4" s="23" t="inlineStr">
+      <c r="G4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">뻑</t>
         </is>
@@ -3495,7 +3515,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I4" s="23" t="inlineStr">
+      <c r="I4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">애</t>
         </is>
@@ -3506,7 +3526,7 @@
 –仲</t>
         </is>
       </c>
-      <c r="K4" s="25" t="inlineStr">
+      <c r="K4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">치</t>
         </is>
@@ -3517,7 +3537,7 @@
 潢</t>
         </is>
       </c>
-      <c r="M4" s="23" t="inlineStr">
+      <c r="M4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">해</t>
         </is>
@@ -3530,7 +3550,7 @@
           <t xml:space="preserve">–㳞</t>
         </is>
       </c>
-      <c r="C5" s="26" t="inlineStr">
+      <c r="C5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
@@ -3540,14 +3560,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E5" s="26"/>
+      <c r="E5" s="31"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –無</t>
         </is>
       </c>
-      <c r="G5" s="26" t="inlineStr">
+      <c r="G5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">자</t>
         </is>
@@ -3557,7 +3577,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I5" s="26" t="inlineStr">
+      <c r="I5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
@@ -3567,7 +3587,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K5" s="26" t="inlineStr">
+      <c r="K5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
@@ -3577,7 +3597,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M5" s="26" t="inlineStr">
+      <c r="M5" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -3590,7 +3610,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
@@ -3600,7 +3620,7 @@
           <t xml:space="preserve">潢姑</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
@@ -3610,7 +3630,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">없</t>
         </is>
@@ -3621,7 +3641,7 @@
 –㳞</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">마</t>
         </is>
@@ -3631,7 +3651,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
@@ -3641,7 +3661,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M6" s="22" t="inlineStr">
+      <c r="M6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
@@ -3655,7 +3675,7 @@
 –潢</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
@@ -3666,13 +3686,13 @@
 仲潢</t>
         </is>
       </c>
-      <c r="E7" s="23"/>
+      <c r="E7" s="29"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G7" s="23" t="inlineStr">
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -3683,7 +3703,7 @@
 –㳞</t>
         </is>
       </c>
-      <c r="I7" s="23" t="inlineStr">
+      <c r="I7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">음
 은</t>
@@ -3695,7 +3715,7 @@
 –姑</t>
         </is>
       </c>
-      <c r="K7" s="23" t="inlineStr">
+      <c r="K7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -3706,7 +3726,7 @@
 潢</t>
         </is>
       </c>
-      <c r="M7" s="23" t="inlineStr">
+      <c r="M7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">산</t>
         </is>
@@ -3720,7 +3740,7 @@
 –無</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
@@ -3731,7 +3751,7 @@
 潢</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -3742,7 +3762,7 @@
 –姑</t>
         </is>
       </c>
-      <c r="G8" s="26" t="inlineStr">
+      <c r="G8" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">서</t>
         </is>
@@ -3753,13 +3773,13 @@
 △</t>
         </is>
       </c>
-      <c r="I8" s="26"/>
+      <c r="I8" s="31"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="K8" s="26" t="inlineStr">
+      <c r="K8" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">만</t>
         </is>
@@ -3770,7 +3790,7 @@
 無</t>
         </is>
       </c>
-      <c r="M8" s="26" t="inlineStr">
+      <c r="M8" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
@@ -3783,7 +3803,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">좋</t>
         </is>
@@ -3793,7 +3813,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -3803,7 +3823,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">전</t>
         </is>
@@ -3814,7 +3834,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">인</t>
         </is>
@@ -3824,7 +3844,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">인</t>
         </is>
@@ -3834,7 +3854,7 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="M9" s="22" t="inlineStr">
+      <c r="M9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">잣</t>
         </is>
@@ -3848,7 +3868,7 @@
 –姑</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">기
 도</t>
@@ -3859,14 +3879,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E10" s="23"/>
+      <c r="E10" s="29"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –姑</t>
         </is>
       </c>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="G10" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">북
 쌈</t>
@@ -3878,7 +3898,7 @@
 –潢</t>
         </is>
       </c>
-      <c r="I10" s="23" t="inlineStr">
+      <c r="I10" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">심
 도</t>
@@ -3890,7 +3910,7 @@
 –潢</t>
         </is>
       </c>
-      <c r="K10" s="23" t="inlineStr">
+      <c r="K10" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">심
 도</t>
@@ -3902,7 +3922,7 @@
 黃</t>
         </is>
       </c>
-      <c r="M10" s="23" t="inlineStr">
+      <c r="M10" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">나
 무</t>
@@ -3917,7 +3937,7 @@
 –姑</t>
         </is>
       </c>
-      <c r="C11" s="26" t="inlineStr">
+      <c r="C11" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -3927,13 +3947,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E11" s="26"/>
+      <c r="E11" s="31"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G11" s="26" t="inlineStr">
+      <c r="G11" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
         </is>
@@ -3944,7 +3964,7 @@
 –無</t>
         </is>
       </c>
-      <c r="I11" s="26" t="inlineStr">
+      <c r="I11" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">좋
 구</t>
@@ -3956,7 +3976,7 @@
 –姑</t>
         </is>
       </c>
-      <c r="K11" s="26" t="inlineStr">
+      <c r="K11" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">좋
 구</t>
@@ -3968,7 +3988,7 @@
 –姑</t>
         </is>
       </c>
-      <c r="M11" s="26" t="inlineStr">
+      <c r="M11" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">그</t>
         </is>
@@ -3981,7 +4001,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -3991,13 +4011,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E12" s="22"/>
+      <c r="E12" s="28"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
@@ -4008,7 +4028,7 @@
 無</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
@@ -4018,7 +4038,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="K12" s="22" t="inlineStr">
+      <c r="K12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
@@ -4028,7 +4048,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="M12" s="22" t="inlineStr">
+      <c r="M12" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">늘</t>
         </is>
@@ -4041,38 +4061,38 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C13" s="23"/>
+      <c r="C13" s="29"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E13" s="23"/>
+      <c r="E13" s="29"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G13" s="23"/>
+      <c r="G13" s="29"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –姑</t>
         </is>
       </c>
-      <c r="I13" s="23"/>
+      <c r="I13" s="29"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K13" s="23"/>
+      <c r="K13" s="29"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–姑</t>
         </is>
       </c>
-      <c r="M13" s="23"/>
+      <c r="M13" s="29"/>
     </row>
     <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
@@ -4081,37 +4101,37 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C14" s="27"/>
+      <c r="C14" s="32"/>
       <c r="D14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E14" s="27"/>
+      <c r="E14" s="32"/>
       <c r="F14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G14" s="27"/>
+      <c r="G14" s="32"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="I14" s="26"/>
+      <c r="I14" s="31"/>
       <c r="J14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K14" s="27"/>
+      <c r="K14" s="32"/>
       <c r="L14" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">仲姑</t>
         </is>
       </c>
-      <c r="M14" s="27"/>
+      <c r="M14" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/울산 아가씨.xlsx
+++ b/sheets/민요/검수/울산 아가씨.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -217,6 +212,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -226,31 +227,19 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -351,7 +340,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">72</t>
+          <t xml:space="preserve">76</t>
         </is>
       </c>
     </row>
@@ -363,7 +352,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
     </row>
@@ -375,7 +364,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
     </row>
@@ -387,7 +376,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">상</t>
+          <t xml:space="preserve">중</t>
         </is>
       </c>
     </row>
@@ -397,7 +386,11 @@
           <t xml:space="preserve">확인 필요</t>
         </is>
       </c>
-      <c r="B12" s="4"/>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">팔레트 외 글자 1</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="0"/>
@@ -423,7 +416,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">12정간, 굿거리(3/4). 머리 오른쪽 "굿거리 C키", 제목 "울산 아가씨". 내용 6줄(오른쪽=1). 가사 전사 완료(각 율명열 바로 오른쪽 좁은 칸). 1~5줄 1절("동해나 을산은 잣나무 그늘 / 경치도 좋지만 인심도 좋구요 / 큰애기 마음은 인심도 좋구요 / 실뻑자 없어서 전북쌈일세 / 에 헤 에 아…"), 6줄 2절("동해라 을산은 좋기도 하다"). 요성 물결선·작은 꾸밈 생략. 하단 ○ 종지. 손글씨 흘림으로 일부 율명 추정. AI 재판독.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 12정간(굵은 선 3칸마다) 3/4, 7줄(오른쪽=1). 오른쪽 위 "굿거리 C키"(기존 #키 C# 유지), 제목 "울산 아가씨"(아가씨 앞 덧쓴 글자 지움). 가사는 각 율명 줄 오른쪽 칸: 1줄 동해나 울산은 잣나무 그늘, 2줄 경치도 좋지만 인심도 좋구요, 3줄 큰애기 마음은 인심도 좋구요, 4줄 실뻑자 없어서 전복쌈일세, 5줄 에헤에아(후렴), 6줄 동해라 을산은 좋기도 하다. 7줄은 1~4정간에만 표시(작은 점·선, 潢|–?)가 있고 나머지 빈칸. 한 곡. 율명 옆 작은 ^ 꾸밈은 無^ 로 적음.</t>
         </is>
       </c>
     </row>
@@ -650,18 +643,18 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|潢</t>
+          <t xml:space="preserve">潢|–潢</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">해</t>
+          <t xml:space="preserve">해나</t>
         </is>
       </c>
       <c r="J3" s="4"/>
@@ -698,11 +691,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나</t>
-        </is>
-      </c>
+      <c r="I4" s="2"/>
       <c r="J4" s="4"/>
       <c r="K4" s="2"/>
     </row>
@@ -739,7 +728,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">은</t>
+          <t xml:space="preserve">울</t>
         </is>
       </c>
       <c r="J5" s="4"/>
@@ -768,13 +757,13 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|潢</t>
+          <t xml:space="preserve">無|–㴌</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-潢</t>
+–㴌</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -808,13 +797,13 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|無</t>
+          <t xml:space="preserve">潢|–無</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-無</t>
+–無</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -887,13 +876,13 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|黃</t>
+          <t xml:space="preserve">無|–潢</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-黃</t>
+–潢</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1006,12 +995,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–姑</t>
+          <t xml:space="preserve">–|–姑</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–姑</t>
+          <t xml:space="preserve">–
+–姑</t>
         </is>
       </c>
       <c r="I12" s="2"/>
@@ -1039,22 +1029,19 @@
       <c r="F13" s="2">
         <v>4</v>
       </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲姑</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲姑</t>
-        </is>
-      </c>
-      <c r="I13" s="3"/>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">종지 ○</t>
-        </is>
-      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲|姑</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="I13" s="2"/>
+      <c r="J13" s="4"/>
       <c r="K13" s="2"/>
     </row>
     <row r="14">
@@ -1117,27 +1104,23 @@
       <c r="F15" s="2">
         <v>1</v>
       </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑|–仲</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –仲</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">치</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">첫 글자 女방 흘림, 姑로 봄</t>
-        </is>
-      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">치도</t>
+        </is>
+      </c>
+      <c r="J15" s="4"/>
       <c r="K15" s="2"/>
     </row>
     <row r="16">
@@ -1171,11 +1154,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도</t>
-        </is>
-      </c>
+      <c r="I16" s="2"/>
       <c r="J16" s="4"/>
       <c r="K16" s="2"/>
     </row>
@@ -1359,12 +1338,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|–潢</t>
+          <t xml:space="preserve">無^|–潢</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
+          <t xml:space="preserve">無^
 –潢</t>
         </is>
       </c>
@@ -1478,12 +1457,12 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I24" s="2"/>
@@ -1511,22 +1490,19 @@
       <c r="F25" s="2">
         <v>4</v>
       </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I25" s="3"/>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">종지 ○</t>
-        </is>
-      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I25" s="2"/>
+      <c r="J25" s="4"/>
       <c r="K25" s="2"/>
     </row>
     <row r="26">
@@ -1602,7 +1578,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">애</t>
+          <t xml:space="preserve">애기</t>
         </is>
       </c>
       <c r="J27" s="4"/>
@@ -1639,11 +1615,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기</t>
-        </is>
-      </c>
+      <c r="I28" s="2"/>
       <c r="J28" s="4"/>
       <c r="K28" s="2"/>
     </row>
@@ -1786,13 +1758,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|㳞</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-㳞</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1826,13 +1797,13 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|–潢</t>
+          <t xml:space="preserve">潢|–㴌</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-–潢</t>
+–㴌</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
@@ -1906,13 +1877,13 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|無</t>
+          <t xml:space="preserve">南無|–</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-無</t>
+          <t xml:space="preserve">南無
+–</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -1944,19 +1915,23 @@
       <c r="F36" s="2">
         <v>4</v>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">–|–姑</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –姑</t>
         </is>
       </c>
-      <c r="I36" s="2"/>
-      <c r="J36" s="4"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">– 위 작은 점 두 개 있음</t>
+        </is>
+      </c>
       <c r="K36" s="2"/>
     </row>
     <row r="37">
@@ -1982,12 +1957,14 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲姑</t>
+          <t xml:space="preserve">仲姑|–|△</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲姑</t>
+          <t xml:space="preserve">仲姑
+–
+△</t>
         </is>
       </c>
       <c r="I37" s="2"/>
@@ -2056,13 +2033,13 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|–潢</t>
+          <t xml:space="preserve">無|–㴌</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-–潢</t>
+–㴌</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
@@ -2214,12 +2191,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|–姑</t>
+          <t xml:space="preserve">無^|–姑</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
+          <t xml:space="preserve">無^
 –姑</t>
         </is>
       </c>
@@ -2293,18 +2270,18 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|–姑</t>
+          <t xml:space="preserve">無^|–姑</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無
+          <t xml:space="preserve">無^
 –姑</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">북쌈</t>
+          <t xml:space="preserve">복쌈</t>
         </is>
       </c>
       <c r="J45" s="4"/>
@@ -2331,22 +2308,26 @@
       <c r="F46" s="2">
         <v>3</v>
       </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黃</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黃</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">일</t>
         </is>
       </c>
-      <c r="J46" s="4"/>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변 없음, 黃로 봄</t>
+        </is>
+      </c>
       <c r="K46" s="2"/>
     </row>
     <row r="47">
@@ -2411,12 +2392,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I48" s="2"/>
@@ -2444,22 +2425,19 @@
       <c r="F49" s="2">
         <v>4</v>
       </c>
-      <c r="G49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I49" s="3"/>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">종지 ○</t>
-        </is>
-      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I49" s="2"/>
+      <c r="J49" s="4"/>
       <c r="K49" s="2"/>
     </row>
     <row r="50">
@@ -2524,12 +2502,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I51" s="2"/>
@@ -2592,22 +2570,26 @@
       <c r="F53" s="2">
         <v>2</v>
       </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢姑</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢姑</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">헤</t>
         </is>
       </c>
-      <c r="J53" s="4"/>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 혜로 씀</t>
+        </is>
+      </c>
       <c r="K53" s="2"/>
     </row>
     <row r="54">
@@ -2631,19 +2613,23 @@
       <c r="F54" s="2">
         <v>2</v>
       </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|仲潢</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|㴌</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-仲潢</t>
-        </is>
-      </c>
-      <c r="I54" s="2"/>
-      <c r="J54" s="4"/>
+㴌</t>
+        </is>
+      </c>
+      <c r="I54" s="3"/>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞 위에 㴌 덧씀, 㴌로 봄</t>
+        </is>
+      </c>
       <c r="K54" s="2"/>
     </row>
     <row r="55">
@@ -2669,13 +2655,13 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|潢</t>
+          <t xml:space="preserve">潢|–㴌</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-潢</t>
+–㴌</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -2748,12 +2734,12 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I57" s="2"/>
@@ -2783,12 +2769,12 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I58" s="2"/>
@@ -2818,12 +2804,12 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I59" s="2"/>
@@ -2886,22 +2872,19 @@
       <c r="F61" s="2">
         <v>4</v>
       </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H61" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I61" s="3"/>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">종지 ○</t>
-        </is>
-      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I61" s="2"/>
+      <c r="J61" s="4"/>
       <c r="K61" s="2"/>
     </row>
     <row r="62">
@@ -2927,12 +2910,12 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3005,12 +2988,13 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–㳞</t>
+          <t xml:space="preserve">–|㴌</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–㳞</t>
+          <t xml:space="preserve">–
+㴌</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3042,22 +3026,26 @@
       <c r="F65" s="2">
         <v>2</v>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G65" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="H65" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
+      <c r="I65" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="J65" s="4"/>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 이미지대로 을(1줄은 울)</t>
+        </is>
+      </c>
       <c r="K65" s="2"/>
     </row>
     <row r="66">
@@ -3083,13 +3071,13 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|–潢</t>
+          <t xml:space="preserve">無|–㴌</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-–潢</t>
+–㴌</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3354,26 +3342,176 @@
       <c r="F73" s="2">
         <v>4</v>
       </c>
-      <c r="G73" s="3" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I73" s="2"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="2"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2">
+        <v>1</v>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/울산 아가씨.png</t>
+        </is>
+      </c>
+      <c r="C74" s="2">
+        <v>7</v>
+      </c>
+      <c r="D74" s="2">
+        <v>7</v>
+      </c>
+      <c r="E74" s="2">
+        <v>1</v>
+      </c>
+      <c r="F74" s="2">
+        <v>1</v>
+      </c>
+      <c r="G74" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="H73" s="3" t="inlineStr">
+      <c r="H74" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I73" s="3"/>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">종지 ○</t>
-        </is>
-      </c>
-      <c r="K73" s="2"/>
+      <c r="I74" s="3"/>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작은 점, 얼룩일 수도</t>
+        </is>
+      </c>
+      <c r="K74" s="2"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2">
+        <v>1</v>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/울산 아가씨.png</t>
+        </is>
+      </c>
+      <c r="C75" s="2">
+        <v>7</v>
+      </c>
+      <c r="D75" s="2">
+        <v>7</v>
+      </c>
+      <c r="E75" s="2">
+        <v>2</v>
+      </c>
+      <c r="F75" s="2">
+        <v>1</v>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I75" s="2"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="2"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2">
+        <v>1</v>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/울산 아가씨.png</t>
+        </is>
+      </c>
+      <c r="C76" s="2">
+        <v>7</v>
+      </c>
+      <c r="D76" s="2">
+        <v>7</v>
+      </c>
+      <c r="E76" s="2">
+        <v>3</v>
+      </c>
+      <c r="F76" s="2">
+        <v>1</v>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I76" s="2"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="2"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2">
+        <v>1</v>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-3/울산 아가씨.png</t>
+        </is>
+      </c>
+      <c r="C77" s="2">
+        <v>7</v>
+      </c>
+      <c r="D77" s="2">
+        <v>7</v>
+      </c>
+      <c r="E77" s="2">
+        <v>4</v>
+      </c>
+      <c r="F77" s="2">
+        <v>2</v>
+      </c>
+      <c r="G77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢|–?</t>
+        </is>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–?</t>
+        </is>
+      </c>
+      <c r="I77" s="5"/>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아래 글자 ㄴ+氵+巳 모양, 㴌/無? 판독 불가</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">?</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K73"/>
+  <autoFilter ref="A1:K77"/>
 </worksheet>
 </file>
 
@@ -3393,12 +3531,14 @@
     <col min="11" max="11" width="6" customWidth="1"/>
     <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="55.19" customHeight="1">
+    <row r="2" ht="77.61" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3416,729 +3556,771 @@
       <c r="K2" s="20"/>
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
-    </row>
-    <row r="3" ht="55.19" customHeight="1">
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+    </row>
+    <row r="3" ht="77.61" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C3" s="22"/>
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">동</t>
+        </is>
+      </c>
+      <c r="F3" s="23" t="inlineStr">
+        <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C3" s="28" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
+      <c r="H3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">실</t>
+        </is>
+      </c>
+      <c r="J3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="K3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">큰</t>
+        </is>
+      </c>
+      <c r="L3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黃</t>
+        </is>
+      </c>
+      <c r="M3" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">경</t>
+        </is>
+      </c>
+      <c r="N3" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">동</t>
         </is>
       </c>
-      <c r="D3" s="21" t="inlineStr">
+    </row>
+    <row r="4" ht="77.61" customHeight="1">
+      <c r="A4" s="0"/>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C4" s="25"/>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G4" s="25"/>
+      <c r="H4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–㴌</t>
+        </is>
+      </c>
+      <c r="I4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">뻑</t>
+        </is>
+      </c>
+      <c r="J4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+潢</t>
+        </is>
+      </c>
+      <c r="K4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">애
+기</t>
+        </is>
+      </c>
+      <c r="L4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑
+–仲</t>
+        </is>
+      </c>
+      <c r="M4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">치
+도</t>
+        </is>
+      </c>
+      <c r="N4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–潢</t>
+        </is>
+      </c>
+      <c r="O4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">해
+나</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="77.61" customHeight="1">
+      <c r="A5" s="0"/>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="C5" s="26"/>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+㴌</t>
+        </is>
+      </c>
+      <c r="E5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">라</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G5" s="26"/>
+      <c r="H5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–無</t>
+        </is>
+      </c>
+      <c r="I5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">자</t>
+        </is>
+      </c>
+      <c r="J5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K5" s="26"/>
+      <c r="L5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M5" s="26"/>
+      <c r="N5" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="O5" s="26"/>
+    </row>
+    <row r="6" ht="77.61" customHeight="1">
+      <c r="A6" s="0"/>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–?</t>
+        </is>
+      </c>
+      <c r="C6" s="28"/>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E3" s="28" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">헤</t>
+        </is>
+      </c>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="I6" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">없</t>
+        </is>
+      </c>
+      <c r="J6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–㳞</t>
+        </is>
+      </c>
+      <c r="K6" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마</t>
+        </is>
+      </c>
+      <c r="L6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="M6" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">좋</t>
+        </is>
+      </c>
+      <c r="N6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="O6" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">울</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="77.61" customHeight="1">
+      <c r="A7" s="0"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–㴌</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">산</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+㴌</t>
+        </is>
+      </c>
+      <c r="G7" s="29"/>
+      <c r="H7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="J7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞
+–㳞</t>
+        </is>
+      </c>
+      <c r="K7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">음
+은</t>
+        </is>
+      </c>
+      <c r="L7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–姑</t>
+        </is>
+      </c>
+      <c r="M7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지</t>
+        </is>
+      </c>
+      <c r="N7" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–㴌</t>
+        </is>
+      </c>
+      <c r="O7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">산</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="77.61" customHeight="1">
+      <c r="A8" s="0"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–無</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">은</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–㴌</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G3" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">실</t>
-        </is>
-      </c>
-      <c r="H3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I3" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">큰</t>
-        </is>
-      </c>
-      <c r="J3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">黃</t>
-        </is>
-      </c>
-      <c r="K3" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">경</t>
-        </is>
-      </c>
-      <c r="L3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M3" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">동</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="55.19" customHeight="1">
-      <c r="A4" s="0"/>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無^
+–姑</t>
+        </is>
+      </c>
+      <c r="I8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">서</t>
+        </is>
+      </c>
+      <c r="J8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="K8" s="26"/>
+      <c r="L8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲姑</t>
+        </is>
+      </c>
+      <c r="M8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">만</t>
+        </is>
+      </c>
+      <c r="N8" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–無</t>
+        </is>
+      </c>
+      <c r="O8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">은</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="77.61" customHeight="1">
+      <c r="A9" s="0"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">좋</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">해</t>
-        </is>
-      </c>
-      <c r="D4" s="21" t="inlineStr">
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아</t>
+        </is>
+      </c>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">전</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㴌</t>
+        </is>
+      </c>
+      <c r="K9" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">인</t>
+        </is>
+      </c>
+      <c r="L9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無</t>
+        </is>
+      </c>
+      <c r="M9" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">인</t>
+        </is>
+      </c>
+      <c r="N9" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">姑</t>
+        </is>
+      </c>
+      <c r="O9" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잣</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="77.61" customHeight="1">
+      <c r="A10" s="0"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無
+–姑</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">기
+도</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="29"/>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="G10" s="25"/>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無^
+–姑</t>
+        </is>
+      </c>
+      <c r="I10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">복
+쌈</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢
+–㴌</t>
+        </is>
+      </c>
+      <c r="K10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">심
+도</t>
+        </is>
+      </c>
+      <c r="L10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">無^
+–潢</t>
+        </is>
+      </c>
+      <c r="M10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">심
+도</t>
+        </is>
+      </c>
+      <c r="N10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –潢</t>
         </is>
       </c>
-      <c r="G4" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">뻑</t>
-        </is>
-      </c>
-      <c r="H4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-潢</t>
-        </is>
-      </c>
-      <c r="I4" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">애</t>
-        </is>
-      </c>
-      <c r="J4" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
-–仲</t>
-        </is>
-      </c>
-      <c r="K4" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">치</t>
-        </is>
-      </c>
-      <c r="L4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-潢</t>
-        </is>
-      </c>
-      <c r="M4" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">해</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="55.19" customHeight="1">
-      <c r="A5" s="0"/>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–㳞</t>
-        </is>
-      </c>
-      <c r="C5" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">라</t>
-        </is>
-      </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="O10" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나
+무</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="77.61" customHeight="1">
+      <c r="A11" s="0"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="26"/>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黃
+–姑</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">하</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="G11" s="26"/>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黃</t>
+        </is>
+      </c>
+      <c r="I11" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">일</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –無</t>
         </is>
       </c>
-      <c r="G5" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">자</t>
-        </is>
-      </c>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I5" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기</t>
-        </is>
-      </c>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K5" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도</t>
-        </is>
-      </c>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="M5" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="55.19" customHeight="1">
-      <c r="A6" s="0"/>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="C6" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">을</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢姑</t>
-        </is>
-      </c>
-      <c r="E6" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">헤</t>
-        </is>
-      </c>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="G6" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">없</t>
-        </is>
-      </c>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-–㳞</t>
-        </is>
-      </c>
-      <c r="I6" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">마</t>
-        </is>
-      </c>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="K6" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">좋</t>
-        </is>
-      </c>
-      <c r="L6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="M6" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">은</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="55.19" customHeight="1">
-      <c r="A7" s="0"/>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-–潢</t>
-        </is>
-      </c>
-      <c r="C7" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">산</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-仲潢</t>
-        </is>
-      </c>
-      <c r="E7" s="29"/>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="G7" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">어</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞
-–㳞</t>
-        </is>
-      </c>
-      <c r="I7" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">음
-은</t>
-        </is>
-      </c>
-      <c r="J7" s="21" t="inlineStr">
+      <c r="K11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">좋
+구</t>
+        </is>
+      </c>
+      <c r="L11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –姑</t>
         </is>
       </c>
-      <c r="K7" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">지</t>
-        </is>
-      </c>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-潢</t>
-        </is>
-      </c>
-      <c r="M7" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">산</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="55.19" customHeight="1">
-      <c r="A8" s="0"/>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-–無</t>
-        </is>
-      </c>
-      <c r="C8" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">은</t>
-        </is>
-      </c>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-潢</t>
-        </is>
-      </c>
-      <c r="E8" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="M11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">좋
+구</t>
+        </is>
+      </c>
+      <c r="N11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –姑</t>
         </is>
       </c>
-      <c r="G8" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">서</t>
-        </is>
-      </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="O11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="77.61" customHeight="1">
+      <c r="A12" s="0"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G12" s="24"/>
+      <c r="H12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">세</t>
+        </is>
+      </c>
+      <c r="J12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南無
+–</t>
+        </is>
+      </c>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요</t>
+        </is>
+      </c>
+      <c r="L12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="M12" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">요</t>
+        </is>
+      </c>
+      <c r="N12" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="O12" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">늘</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="77.61" customHeight="1">
+      <c r="A13" s="0"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="E13" s="25"/>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="G13" s="25"/>
+      <c r="H13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I13" s="25"/>
+      <c r="J13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+–姑</t>
+        </is>
+      </c>
+      <c r="K13" s="29"/>
+      <c r="L13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M13" s="25"/>
+      <c r="N13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+–姑</t>
+        </is>
+      </c>
+      <c r="O13" s="25"/>
+    </row>
+    <row r="14" ht="77.61" customHeight="1">
+      <c r="A14" s="0"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="I8" s="31"/>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲姑</t>
-        </is>
-      </c>
-      <c r="K8" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">만</t>
-        </is>
-      </c>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-無</t>
-        </is>
-      </c>
-      <c r="M8" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">은</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="55.19" customHeight="1">
-      <c r="A9" s="0"/>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="C9" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">좋</t>
-        </is>
-      </c>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞</t>
-        </is>
-      </c>
-      <c r="E9" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="G9" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">전</t>
-        </is>
-      </c>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-㳞</t>
-        </is>
-      </c>
-      <c r="I9" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">인</t>
-        </is>
-      </c>
-      <c r="J9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無</t>
-        </is>
-      </c>
-      <c r="K9" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">인</t>
-        </is>
-      </c>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑</t>
-        </is>
-      </c>
-      <c r="M9" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">잣</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="55.19" customHeight="1">
-      <c r="A10" s="0"/>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-–姑</t>
-        </is>
-      </c>
-      <c r="C10" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">기
-도</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E10" s="29"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-–姑</t>
-        </is>
-      </c>
-      <c r="G10" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">북
-쌈</t>
-        </is>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-–潢</t>
-        </is>
-      </c>
-      <c r="I10" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">심
-도</t>
-        </is>
-      </c>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-–潢</t>
-        </is>
-      </c>
-      <c r="K10" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">심
-도</t>
-        </is>
-      </c>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-黃</t>
-        </is>
-      </c>
-      <c r="M10" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나
-무</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="55.19" customHeight="1">
-      <c r="A11" s="0"/>
-      <c r="B11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">黃
-–姑</t>
-        </is>
-      </c>
-      <c r="C11" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G11" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">일</t>
-        </is>
-      </c>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-–無</t>
-        </is>
-      </c>
-      <c r="I11" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">좋
-구</t>
-        </is>
-      </c>
-      <c r="J11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-–姑</t>
-        </is>
-      </c>
-      <c r="K11" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">좋
-구</t>
-        </is>
-      </c>
-      <c r="L11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">無
-–姑</t>
-        </is>
-      </c>
-      <c r="M11" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="55.19" customHeight="1">
-      <c r="A12" s="0"/>
-      <c r="B12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C12" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">다</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E12" s="28"/>
-      <c r="F12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="G12" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">세</t>
-        </is>
-      </c>
-      <c r="H12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">南
-無</t>
-        </is>
-      </c>
-      <c r="I12" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요</t>
-        </is>
-      </c>
-      <c r="J12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="K12" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">요</t>
-        </is>
-      </c>
-      <c r="L12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="M12" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">늘</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="55.19" customHeight="1">
-      <c r="A13" s="0"/>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E13" s="29"/>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G13" s="29"/>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="E14" s="26"/>
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–姑</t>
-        </is>
-      </c>
-      <c r="I13" s="29"/>
-      <c r="J13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K13" s="29"/>
-      <c r="L13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–姑</t>
-        </is>
-      </c>
-      <c r="M13" s="29"/>
-    </row>
-    <row r="14" ht="55.19" customHeight="1">
-      <c r="A14" s="0"/>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C14" s="32"/>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="E14" s="32"/>
-      <c r="F14" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="G14" s="32"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲姑</t>
-        </is>
-      </c>
-      <c r="I14" s="31"/>
-      <c r="J14" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K14" s="32"/>
-      <c r="L14" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲姑</t>
-        </is>
-      </c>
-      <c r="M14" s="32"/>
+△</t>
+        </is>
+      </c>
+      <c r="G14" s="26"/>
+      <c r="H14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I14" s="26"/>
+      <c r="J14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲姑
+–
+△</t>
+        </is>
+      </c>
+      <c r="K14" s="26"/>
+      <c r="L14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="M14" s="26"/>
+      <c r="N14" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲
+姑</t>
+        </is>
+      </c>
+      <c r="O14" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B2:M2"/>
+    <mergeCell ref="B2:O2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="86"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/울산 아가씨.xlsx
+++ b/sheets/민요/검수/울산 아가씨.xlsx
@@ -416,7 +416,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 12정간(굵은 선 3칸마다) 3/4, 7줄(오른쪽=1). 오른쪽 위 "굿거리 C키"(기존 #키 C# 유지), 제목 "울산 아가씨"(아가씨 앞 덧쓴 글자 지움). 가사는 각 율명 줄 오른쪽 칸: 1줄 동해나 울산은 잣나무 그늘, 2줄 경치도 좋지만 인심도 좋구요, 3줄 큰애기 마음은 인심도 좋구요, 4줄 실뻑자 없어서 전복쌈일세, 5줄 에헤에아(후렴), 6줄 동해라 을산은 좋기도 하다. 7줄은 1~4정간에만 표시(작은 점·선, 潢|–?)가 있고 나머지 빈칸. 한 곡. 율명 옆 작은 ^ 꾸밈은 無^ 로 적음.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 12정간(굵은 선 3칸마다) 3/4, 7줄(오른쪽=1). 오른쪽 위 "굿거리 C키"(기존 #키 C# 유지), 제목 "울산 아가씨"(아가씨 앞 덧쓴 글자 지움). 가사는 각 율명 줄 오른쪽 칸: 1줄 동해나 울산은 잣나무 그늘, 2줄 경치도 좋지만 인심도 좋구요, 3줄 큰애기 마음은 인심도 좋구요, 4줄 실뻑자 없어서 전복쌈일세, 5줄 에헤에아(후렴), 6줄 동해라 을산은 좋기도 하다. 7줄은 1~4정간에만 표시(작은 점·선, 潢|–?)가 있고 나머지 빈칸. 한 곡. 율명 옆 작은 ^ 꾸밈은 無^ 로 적음. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -916,13 +916,13 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|–姑</t>
+          <t xml:space="preserve">無|–南</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-–姑</t>
+–南</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,13 +995,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|–姑</t>
+          <t xml:space="preserve">–|–南</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–姑</t>
+–南</t>
         </is>
       </c>
       <c r="I12" s="2"/>
@@ -1031,13 +1031,13 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲|姑</t>
+          <t xml:space="preserve">仲|南</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-姑</t>
+南</t>
         </is>
       </c>
       <c r="I13" s="2"/>
@@ -1220,13 +1220,13 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|–姑</t>
+          <t xml:space="preserve">無|–南</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-–姑</t>
+–南</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲姑</t>
+          <t xml:space="preserve">仲南</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲姑</t>
+          <t xml:space="preserve">仲南</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -1378,13 +1378,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|–姑</t>
+          <t xml:space="preserve">無|–南</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-–姑</t>
+–南</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1917,13 +1917,13 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|–姑</t>
+          <t xml:space="preserve">–|–南</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–姑</t>
+–南</t>
         </is>
       </c>
       <c r="I36" s="3"/>
@@ -1957,12 +1957,12 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲姑|–|△</t>
+          <t xml:space="preserve">仲南|–|△</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲姑
+          <t xml:space="preserve">仲南
 –
 △</t>
         </is>
@@ -2113,12 +2113,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2191,13 +2191,13 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無^|–姑</t>
+          <t xml:space="preserve">無^|–南</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無^
-–姑</t>
+–南</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -2270,13 +2270,13 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無^|–姑</t>
+          <t xml:space="preserve">無^|–南</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無^
-–姑</t>
+–南</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3190,13 +3190,13 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|–姑</t>
+          <t xml:space="preserve">無|–南</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-–姑</t>
+–南</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="H6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="I6" s="24" t="inlineStr">
@@ -3873,7 +3873,7 @@
       <c r="L7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-–姑</t>
+–南</t>
         </is>
       </c>
       <c r="M7" s="25" t="inlineStr">
@@ -3922,7 +3922,7 @@
       <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無^
-–姑</t>
+–南</t>
         </is>
       </c>
       <c r="I8" s="26" t="inlineStr">
@@ -3939,7 +3939,7 @@
       <c r="K8" s="26"/>
       <c r="L8" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲姑</t>
+          <t xml:space="preserve">仲南</t>
         </is>
       </c>
       <c r="M8" s="26" t="inlineStr">
@@ -3965,7 +3965,7 @@
       <c r="C9" s="24"/>
       <c r="D9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="N9" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="O9" s="24" t="inlineStr">
@@ -4031,7 +4031,7 @@
       <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-–姑</t>
+–南</t>
         </is>
       </c>
       <c r="E10" s="25" t="inlineStr">
@@ -4049,7 +4049,7 @@
       <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無^
-–姑</t>
+–南</t>
         </is>
       </c>
       <c r="I10" s="25" t="inlineStr">
@@ -4141,7 +4141,7 @@
       <c r="L11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-–姑</t>
+–南</t>
         </is>
       </c>
       <c r="M11" s="26" t="inlineStr">
@@ -4153,7 +4153,7 @@
       <c r="N11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-–姑</t>
+–南</t>
         </is>
       </c>
       <c r="O11" s="26" t="inlineStr">
@@ -4249,7 +4249,7 @@
       <c r="J13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–姑</t>
+–南</t>
         </is>
       </c>
       <c r="K13" s="29"/>
@@ -4262,7 +4262,7 @@
       <c r="N13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–姑</t>
+–南</t>
         </is>
       </c>
       <c r="O13" s="25"/>
@@ -4294,7 +4294,7 @@
       <c r="I14" s="26"/>
       <c r="J14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲姑
+          <t xml:space="preserve">仲南
 –
 △</t>
         </is>
@@ -4310,7 +4310,7 @@
       <c r="N14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲
-姑</t>
+南</t>
         </is>
       </c>
       <c r="O14" s="26"/>

--- a/sheets/민요/검수/울산 아가씨.xlsx
+++ b/sheets/민요/검수/울산 아가씨.xlsx
@@ -596,10 +596,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/울산 아가씨.xlsx
+++ b/sheets/민요/검수/울산 아가씨.xlsx
@@ -563,13 +563,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="24"/>
       <name val="궁서체"/>
       <family val="2"/>
@@ -581,8 +574,15 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -594,9 +594,6 @@
         <fgColor rgb="FFD9D9D9"/>
         <bgColor rgb="FFF8CBAD"/>
       </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -675,76 +672,64 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -757,7 +742,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -777,14 +762,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF8CBAD"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFF2CC"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -810,7 +787,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF2CC"/>
+      <rgbColor rgb="FFFFFFCC"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -971,171 +948,171 @@
   <dimension ref="A1:B23"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="90"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="90"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
+      <c r="B1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3"/>
+      <c r="B5" s="4"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="65.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="3" t="s">
+      <c r="A15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="1"/>
+      <c r="B17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="65.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="4" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1158,2368 +1135,2368 @@
   <dimension ref="A1:K77"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="J2" s="3"/>
-      <c r="K2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="4" t="s">
+      <c r="A3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="4" t="s">
+      <c r="A4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="4"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" s="4" t="s">
+      <c r="A5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4" t="n">
+      <c r="A6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="F6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4" t="n">
+      <c r="A7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="F7" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="4" t="n">
+      <c r="A8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F8" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="F8" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G8" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4" t="n">
+      <c r="A9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="F9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="4" t="n">
+      <c r="A10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="F10" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" s="4" t="s">
+      <c r="F10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="4" t="n">
+      <c r="A11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="F11" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G11" s="4" t="s">
+      <c r="F11" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="4" t="n">
+      <c r="A12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="F12" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G12" s="4" t="s">
+      <c r="F12" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="I12" s="4"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="4"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="4" t="n">
+      <c r="A13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="F13" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" s="4" t="s">
+      <c r="F13" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="I13" s="4"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="4"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="4" t="s">
+      <c r="A14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" s="4" t="s">
+      <c r="A15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="4" t="s">
+      <c r="A16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="I16" s="4"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="4"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G17" s="4" t="s">
+      <c r="A17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E18" s="4" t="n">
+      <c r="A18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F18" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" s="4" t="s">
+      <c r="F18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" s="4" t="n">
+      <c r="A19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F19" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G19" s="4" t="s">
+      <c r="F19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" s="4" t="n">
+      <c r="A20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F20" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G20" s="4" t="s">
+      <c r="F20" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E21" s="4" t="n">
+      <c r="A21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F21" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G21" s="4" t="s">
+      <c r="F21" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E22" s="4" t="n">
+      <c r="A22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="F22" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="F22" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H22" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I22" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" s="4" t="n">
+      <c r="A23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="F23" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G23" s="4" t="s">
+      <c r="F23" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" s="4" t="n">
+      <c r="A24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="F24" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G24" s="4" t="s">
+      <c r="F24" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H24" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="I24" s="4"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="4"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" s="4" t="n">
+      <c r="A25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="F25" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G25" s="4" t="s">
+      <c r="F25" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="H25" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="I25" s="4"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="4"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="4" t="s">
+      <c r="A26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H26" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I26" s="4" t="s">
+      <c r="I26" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" s="4" t="s">
+      <c r="A27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H27" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="I27" s="4" t="s">
+      <c r="I27" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="J27" s="3"/>
-      <c r="K27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="4" t="s">
+      <c r="A28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H28" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="I28" s="4"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="4"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="5"/>
     </row>
     <row r="29" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D29" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G29" s="4" t="s">
+      <c r="A29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="H29" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="I29" s="4" t="s">
+      <c r="I29" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="J29" s="3"/>
-      <c r="K29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E30" s="4" t="n">
+      <c r="A30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F30" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G30" s="4" t="s">
+      <c r="F30" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G30" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="H30" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="I30" s="4" t="s">
+      <c r="I30" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="J30" s="3"/>
-      <c r="K30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E31" s="4" t="n">
+      <c r="A31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F31" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G31" s="4" t="s">
+      <c r="F31" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="H31" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="I31" s="4"/>
-      <c r="J31" s="3"/>
-      <c r="K31" s="4"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="5"/>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E32" s="4" t="n">
+      <c r="A32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F32" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G32" s="4" t="s">
+      <c r="F32" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G32" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="H32" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="I32" s="4" t="s">
+      <c r="I32" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="J32" s="3"/>
-      <c r="K32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="5"/>
     </row>
     <row r="33" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E33" s="4" t="n">
+      <c r="A33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F33" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G33" s="4" t="s">
+      <c r="F33" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H33" s="4" t="s">
+      <c r="H33" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="I33" s="4" t="s">
+      <c r="I33" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="J33" s="3"/>
-      <c r="K33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="5"/>
     </row>
     <row r="34" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C34" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D34" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E34" s="4" t="n">
+      <c r="A34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="F34" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G34" s="4" t="s">
+      <c r="F34" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G34" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H34" s="4" t="s">
+      <c r="H34" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="I34" s="4" t="s">
+      <c r="I34" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="J34" s="3"/>
-      <c r="K34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="5"/>
     </row>
     <row r="35" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E35" s="4" t="n">
+      <c r="A35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="F35" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G35" s="4" t="s">
+      <c r="F35" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G35" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="H35" s="4" t="s">
+      <c r="H35" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="I35" s="4" t="s">
+      <c r="I35" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="J35" s="3"/>
-      <c r="K35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="5"/>
     </row>
     <row r="36" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E36" s="4" t="n">
+      <c r="A36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="F36" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G36" s="5" t="s">
+      <c r="F36" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G36" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="H36" s="5" t="s">
+      <c r="H36" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="I36" s="5"/>
-      <c r="J36" s="3" t="s">
+      <c r="I36" s="6"/>
+      <c r="J36" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="K36" s="4"/>
+      <c r="K36" s="5"/>
     </row>
     <row r="37" customFormat="false" ht="33.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E37" s="4" t="n">
+      <c r="A37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="F37" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G37" s="4" t="s">
+      <c r="F37" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G37" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="H37" s="4" t="s">
+      <c r="H37" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="I37" s="4"/>
-      <c r="J37" s="3"/>
-      <c r="K37" s="4"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="5"/>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="4" t="s">
+      <c r="A38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H38" s="4" t="s">
+      <c r="H38" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I38" s="4" t="s">
+      <c r="I38" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="J38" s="3"/>
-      <c r="K38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="5"/>
     </row>
     <row r="39" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="4" t="s">
+      <c r="A39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H39" s="4" t="s">
+      <c r="H39" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="I39" s="4" t="s">
+      <c r="I39" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="J39" s="3"/>
-      <c r="K39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="5"/>
     </row>
     <row r="40" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C40" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D40" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="4" t="s">
+      <c r="A40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H40" s="4" t="s">
+      <c r="H40" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="I40" s="4" t="s">
+      <c r="I40" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="J40" s="3"/>
-      <c r="K40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="5"/>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G41" s="4" t="s">
+      <c r="A41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G41" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="H41" s="4" t="s">
+      <c r="H41" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="I41" s="4" t="s">
+      <c r="I41" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="J41" s="3"/>
-      <c r="K41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="5"/>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C42" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D42" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E42" s="4" t="n">
+      <c r="A42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E42" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F42" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G42" s="4" t="s">
+      <c r="F42" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="H42" s="4" t="s">
+      <c r="H42" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="I42" s="4" t="s">
+      <c r="I42" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="J42" s="3"/>
-      <c r="K42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="5"/>
     </row>
     <row r="43" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C43" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D43" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E43" s="4" t="n">
+      <c r="A43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E43" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F43" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G43" s="4" t="s">
+      <c r="F43" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="H43" s="4" t="s">
+      <c r="H43" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="I43" s="4" t="s">
+      <c r="I43" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="J43" s="3"/>
-      <c r="K43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="5"/>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D44" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E44" s="4" t="n">
+      <c r="A44" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E44" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F44" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G44" s="4" t="s">
+      <c r="F44" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="H44" s="4" t="s">
+      <c r="H44" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="I44" s="4" t="s">
+      <c r="I44" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="J44" s="3"/>
-      <c r="K44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="5"/>
     </row>
     <row r="45" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C45" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D45" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E45" s="4" t="n">
+      <c r="A45" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E45" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F45" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G45" s="4" t="s">
+      <c r="F45" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G45" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="H45" s="4" t="s">
+      <c r="H45" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="I45" s="4" t="s">
+      <c r="I45" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="J45" s="3"/>
-      <c r="K45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="5"/>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C46" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D46" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E46" s="4" t="n">
+      <c r="A46" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E46" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="F46" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G46" s="5" t="s">
+      <c r="F46" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="H46" s="5" t="s">
+      <c r="H46" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="I46" s="5" t="s">
+      <c r="I46" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="J46" s="3" t="s">
+      <c r="J46" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="K46" s="4"/>
+      <c r="K46" s="5"/>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C47" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D47" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E47" s="4" t="n">
+      <c r="A47" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E47" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="F47" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G47" s="4" t="s">
+      <c r="F47" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G47" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="H47" s="4" t="s">
+      <c r="H47" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="I47" s="4" t="s">
+      <c r="I47" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="J47" s="3"/>
-      <c r="K47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="5"/>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C48" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D48" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E48" s="4" t="n">
+      <c r="A48" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="F48" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G48" s="4" t="s">
+      <c r="F48" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G48" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H48" s="4" t="s">
+      <c r="H48" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="I48" s="4"/>
-      <c r="J48" s="3"/>
-      <c r="K48" s="4"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="5"/>
     </row>
     <row r="49" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C49" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D49" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E49" s="4" t="n">
+      <c r="A49" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E49" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="F49" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G49" s="4" t="s">
+      <c r="F49" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G49" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="H49" s="4" t="s">
+      <c r="H49" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="I49" s="4"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="4"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="5"/>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C50" s="4" t="n">
+      <c r="A50" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C50" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D50" s="4" t="n">
+      <c r="D50" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" s="4" t="s">
+      <c r="E50" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="H50" s="4" t="s">
+      <c r="H50" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I50" s="4" t="s">
+      <c r="I50" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="J50" s="3"/>
-      <c r="K50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="5"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C51" s="4" t="n">
+      <c r="A51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C51" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D51" s="4" t="n">
+      <c r="D51" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E51" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F51" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" s="4" t="s">
+      <c r="E51" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H51" s="4" t="s">
+      <c r="H51" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="I51" s="4"/>
-      <c r="J51" s="3"/>
-      <c r="K51" s="4"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="5"/>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C52" s="4" t="n">
+      <c r="A52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C52" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D52" s="4" t="n">
+      <c r="D52" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E52" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F52" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="4" t="s">
+      <c r="E52" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G52" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="H52" s="4" t="s">
+      <c r="H52" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="I52" s="4"/>
-      <c r="J52" s="3"/>
-      <c r="K52" s="4"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="5"/>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C53" s="4" t="n">
+      <c r="A53" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C53" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D53" s="4" t="n">
+      <c r="D53" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E53" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F53" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G53" s="5" t="s">
+      <c r="E53" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G53" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="H53" s="5" t="s">
+      <c r="H53" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="I53" s="5" t="s">
+      <c r="I53" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="J53" s="3" t="s">
+      <c r="J53" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="K53" s="4"/>
+      <c r="K53" s="5"/>
     </row>
     <row r="54" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C54" s="4" t="n">
+      <c r="A54" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C54" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D54" s="4" t="n">
+      <c r="D54" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E54" s="4" t="n">
+      <c r="E54" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F54" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G54" s="5" t="s">
+      <c r="F54" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="H54" s="5" t="s">
+      <c r="H54" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="I54" s="5"/>
-      <c r="J54" s="3" t="s">
+      <c r="I54" s="6"/>
+      <c r="J54" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="K54" s="4"/>
+      <c r="K54" s="5"/>
     </row>
     <row r="55" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C55" s="4" t="n">
+      <c r="A55" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C55" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D55" s="4" t="n">
+      <c r="D55" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E55" s="4" t="n">
+      <c r="E55" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F55" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G55" s="4" t="s">
+      <c r="F55" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G55" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="H55" s="4" t="s">
+      <c r="H55" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="I55" s="4" t="s">
+      <c r="I55" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="J55" s="3"/>
-      <c r="K55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="5"/>
     </row>
     <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C56" s="4" t="n">
+      <c r="A56" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C56" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D56" s="4" t="n">
+      <c r="D56" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E56" s="4" t="n">
+      <c r="E56" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F56" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G56" s="4" t="s">
+      <c r="F56" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G56" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H56" s="4" t="s">
+      <c r="H56" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="I56" s="4" t="s">
+      <c r="I56" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="J56" s="3"/>
-      <c r="K56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="5"/>
     </row>
     <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C57" s="4" t="n">
+      <c r="A57" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C57" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D57" s="4" t="n">
+      <c r="D57" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E57" s="4" t="n">
+      <c r="E57" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F57" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G57" s="4" t="s">
+      <c r="F57" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G57" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H57" s="4" t="s">
+      <c r="H57" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="I57" s="4"/>
-      <c r="J57" s="3"/>
-      <c r="K57" s="4"/>
+      <c r="I57" s="5"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="5"/>
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C58" s="4" t="n">
+      <c r="A58" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C58" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D58" s="4" t="n">
+      <c r="D58" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E58" s="4" t="n">
+      <c r="E58" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="F58" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G58" s="4" t="s">
+      <c r="F58" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G58" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H58" s="4" t="s">
+      <c r="H58" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="I58" s="4"/>
-      <c r="J58" s="3"/>
-      <c r="K58" s="4"/>
+      <c r="I58" s="5"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="5"/>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C59" s="4" t="n">
+      <c r="A59" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C59" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D59" s="4" t="n">
+      <c r="D59" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E59" s="4" t="n">
+      <c r="E59" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="F59" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G59" s="4" t="s">
+      <c r="F59" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G59" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H59" s="4" t="s">
+      <c r="H59" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="I59" s="4"/>
-      <c r="J59" s="3"/>
-      <c r="K59" s="4"/>
+      <c r="I59" s="5"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="5"/>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C60" s="4" t="n">
+      <c r="A60" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C60" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D60" s="4" t="n">
+      <c r="D60" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E60" s="4" t="n">
+      <c r="E60" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="F60" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G60" s="4" t="s">
+      <c r="F60" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G60" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H60" s="4" t="s">
+      <c r="H60" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="I60" s="4"/>
-      <c r="J60" s="3"/>
-      <c r="K60" s="4"/>
+      <c r="I60" s="5"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="5"/>
     </row>
     <row r="61" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C61" s="4" t="n">
+      <c r="A61" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C61" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D61" s="4" t="n">
+      <c r="D61" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E61" s="4" t="n">
+      <c r="E61" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="F61" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G61" s="4" t="s">
+      <c r="F61" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G61" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="H61" s="4" t="s">
+      <c r="H61" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="I61" s="4"/>
-      <c r="J61" s="3"/>
-      <c r="K61" s="4"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="5"/>
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C62" s="4" t="n">
+      <c r="A62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C62" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D62" s="4" t="n">
+      <c r="D62" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E62" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" s="4" t="s">
+      <c r="E62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="H62" s="4" t="s">
+      <c r="H62" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="I62" s="4" t="s">
+      <c r="I62" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="J62" s="3"/>
-      <c r="K62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="5"/>
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C63" s="4" t="n">
+      <c r="A63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C63" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D63" s="4" t="n">
+      <c r="D63" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E63" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F63" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" s="4" t="s">
+      <c r="E63" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="H63" s="4" t="s">
+      <c r="H63" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="I63" s="4" t="s">
+      <c r="I63" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="J63" s="3"/>
-      <c r="K63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="5"/>
     </row>
     <row r="64" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C64" s="4" t="n">
+      <c r="A64" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C64" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D64" s="4" t="n">
+      <c r="D64" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E64" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F64" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" s="4" t="s">
+      <c r="E64" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="H64" s="4" t="s">
+      <c r="H64" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="I64" s="4" t="s">
+      <c r="I64" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="J64" s="3"/>
-      <c r="K64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="5"/>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C65" s="4" t="n">
+      <c r="A65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C65" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D65" s="4" t="n">
+      <c r="D65" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E65" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F65" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G65" s="5" t="s">
+      <c r="E65" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G65" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H65" s="5" t="s">
+      <c r="H65" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I65" s="5" t="s">
+      <c r="I65" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="J65" s="3" t="s">
+      <c r="J65" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="K65" s="4"/>
+      <c r="K65" s="5"/>
     </row>
     <row r="66" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C66" s="4" t="n">
+      <c r="A66" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C66" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D66" s="4" t="n">
+      <c r="D66" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E66" s="4" t="n">
+      <c r="E66" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F66" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G66" s="4" t="s">
+      <c r="F66" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G66" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="H66" s="4" t="s">
+      <c r="H66" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="I66" s="4" t="s">
+      <c r="I66" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J66" s="3"/>
-      <c r="K66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="5"/>
     </row>
     <row r="67" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C67" s="4" t="n">
+      <c r="A67" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C67" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D67" s="4" t="n">
+      <c r="D67" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E67" s="4" t="n">
+      <c r="E67" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="F67" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G67" s="4" t="s">
+      <c r="F67" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G67" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H67" s="4" t="s">
+      <c r="H67" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="I67" s="4" t="s">
+      <c r="I67" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="J67" s="3"/>
-      <c r="K67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="5"/>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C68" s="4" t="n">
+      <c r="A68" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C68" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D68" s="4" t="n">
+      <c r="D68" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E68" s="4" t="n">
+      <c r="E68" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="F68" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G68" s="4" t="s">
+      <c r="F68" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G68" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="H68" s="4" t="s">
+      <c r="H68" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="I68" s="4" t="s">
+      <c r="I68" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="J68" s="3"/>
-      <c r="K68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="5"/>
     </row>
     <row r="69" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C69" s="4" t="n">
+      <c r="A69" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C69" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D69" s="4" t="n">
+      <c r="D69" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E69" s="4" t="n">
+      <c r="E69" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F69" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G69" s="4" t="s">
+      <c r="F69" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G69" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H69" s="4" t="s">
+      <c r="H69" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="I69" s="4" t="s">
+      <c r="I69" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="J69" s="3"/>
-      <c r="K69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="5"/>
     </row>
     <row r="70" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C70" s="4" t="n">
+      <c r="A70" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C70" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D70" s="4" t="n">
+      <c r="D70" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E70" s="4" t="n">
+      <c r="E70" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="F70" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="G70" s="4" t="s">
+      <c r="F70" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G70" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="H70" s="4" t="s">
+      <c r="H70" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="I70" s="4" t="s">
+      <c r="I70" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="J70" s="3"/>
-      <c r="K70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="5"/>
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C71" s="4" t="n">
+      <c r="A71" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C71" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D71" s="4" t="n">
+      <c r="D71" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E71" s="4" t="n">
+      <c r="E71" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="F71" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G71" s="4" t="s">
+      <c r="F71" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G71" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="H71" s="4" t="s">
+      <c r="H71" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="I71" s="4" t="s">
+      <c r="I71" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="J71" s="3"/>
-      <c r="K71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="5"/>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C72" s="4" t="n">
+      <c r="A72" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C72" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D72" s="4" t="n">
+      <c r="D72" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E72" s="4" t="n">
+      <c r="E72" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="F72" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G72" s="4" t="s">
+      <c r="F72" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G72" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H72" s="4" t="s">
+      <c r="H72" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="I72" s="4"/>
-      <c r="J72" s="3"/>
-      <c r="K72" s="4"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="5"/>
     </row>
     <row r="73" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C73" s="4" t="n">
+      <c r="A73" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C73" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="D73" s="4" t="n">
+      <c r="D73" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E73" s="4" t="n">
+      <c r="E73" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="F73" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G73" s="4" t="s">
+      <c r="F73" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G73" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="H73" s="4" t="s">
+      <c r="H73" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="I73" s="4"/>
-      <c r="J73" s="3"/>
-      <c r="K73" s="4"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="5"/>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C74" s="4" t="n">
+      <c r="A74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C74" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D74" s="4" t="n">
+      <c r="D74" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E74" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F74" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="5" t="s">
+      <c r="E74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="H74" s="5" t="s">
+      <c r="H74" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="I74" s="5"/>
-      <c r="J74" s="3" t="s">
+      <c r="I74" s="6"/>
+      <c r="J74" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="K74" s="4"/>
+      <c r="K74" s="5"/>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C75" s="4" t="n">
+      <c r="A75" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C75" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D75" s="4" t="n">
+      <c r="D75" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E75" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F75" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" s="4" t="s">
+      <c r="E75" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H75" s="4" t="s">
+      <c r="H75" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="I75" s="4"/>
-      <c r="J75" s="3"/>
-      <c r="K75" s="4"/>
+      <c r="I75" s="5"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="5"/>
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C76" s="4" t="n">
+      <c r="A76" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C76" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D76" s="4" t="n">
+      <c r="D76" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E76" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F76" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" s="4" t="s">
+      <c r="E76" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="H76" s="4" t="s">
+      <c r="H76" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="I76" s="4"/>
-      <c r="J76" s="3"/>
-      <c r="K76" s="4"/>
+      <c r="I76" s="5"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="5"/>
     </row>
     <row r="77" customFormat="false" ht="22.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C77" s="4" t="n">
+      <c r="A77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C77" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D77" s="4" t="n">
+      <c r="D77" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E77" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F77" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G77" s="6" t="s">
+      <c r="E77" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G77" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="H77" s="6" t="s">
+      <c r="H77" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="I77" s="6"/>
-      <c r="J77" s="3" t="s">
+      <c r="I77" s="7"/>
+      <c r="J77" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="K77" s="6" t="s">
+      <c r="K77" s="7" t="s">
         <v>145</v>
       </c>
     </row>
@@ -3539,490 +3516,490 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:O14"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="9" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="9" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="8" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="9" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="8" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="9" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="8" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="9" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="8" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="9" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="8" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="9" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="7" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="60.61" customHeight="true">
+      <c r="B2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-    </row>
-    <row r="3" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="8" t="s">
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="10"/>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B3" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="10" t="s">
+      <c r="C3" s="12"/>
+      <c r="D3" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="M3" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="N3" s="10" t="s">
+      <c r="N3" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="O3" s="11" t="s">
+      <c r="O3" s="12" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B4" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="10" t="s">
+      <c r="C4" s="13"/>
+      <c r="D4" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="10" t="s">
+      <c r="G4" s="13"/>
+      <c r="H4" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="J4" s="10" t="s">
+      <c r="J4" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="L4" s="10" t="s">
+      <c r="L4" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="M4" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="N4" s="10" t="s">
+      <c r="N4" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="O4" s="12" t="s">
+      <c r="O4" s="13" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="10" t="s">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B5" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="10" t="s">
+      <c r="C5" s="14"/>
+      <c r="D5" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="10" t="s">
+      <c r="G5" s="14"/>
+      <c r="H5" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="J5" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="K5" s="13"/>
-      <c r="L5" s="10" t="s">
+      <c r="K5" s="14"/>
+      <c r="L5" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="M5" s="13"/>
-      <c r="N5" s="10" t="s">
+      <c r="M5" s="14"/>
+      <c r="N5" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="O5" s="13"/>
-    </row>
-    <row r="6" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="14" t="s">
+      <c r="O5" s="14"/>
+    </row>
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B6" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="8" t="s">
+      <c r="C6" s="12"/>
+      <c r="D6" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="12" t="s">
         <v>134</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="K6" s="11" t="s">
+      <c r="K6" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="L6" s="10" t="s">
+      <c r="L6" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="N6" s="10" t="s">
+      <c r="N6" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="O6" s="11" t="s">
+      <c r="O6" s="12" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="10"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="10" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B7" s="11"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="10" t="s">
+      <c r="G7" s="13"/>
+      <c r="H7" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="J7" s="10" t="s">
+      <c r="J7" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="K7" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="L7" s="10" t="s">
+      <c r="L7" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="M7" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="N7" s="10" t="s">
+      <c r="N7" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="O7" s="12" t="s">
+      <c r="O7" s="13" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="10"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="10" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B8" s="11"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="I8" s="13" t="s">
+      <c r="I8" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="J8" s="10" t="s">
+      <c r="J8" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="K8" s="13"/>
-      <c r="L8" s="10" t="s">
+      <c r="K8" s="14"/>
+      <c r="L8" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="M8" s="13" t="s">
+      <c r="M8" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="N8" s="10" t="s">
+      <c r="N8" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="O8" s="13" t="s">
+      <c r="O8" s="14" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="10"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="10" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B9" s="11"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="G9" s="11" t="s">
+      <c r="G9" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="I9" s="11" t="s">
+      <c r="I9" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="J9" s="10" t="s">
+      <c r="J9" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="L9" s="10" t="s">
+      <c r="L9" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="M9" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="N9" s="10" t="s">
+      <c r="N9" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="O9" s="11" t="s">
+      <c r="O9" s="12" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="10"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="10" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B10" s="11"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="F10" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="12"/>
-      <c r="H10" s="10" t="s">
+      <c r="G10" s="13"/>
+      <c r="H10" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="J10" s="10" t="s">
+      <c r="J10" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="K10" s="12" t="s">
+      <c r="K10" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="L10" s="10" t="s">
+      <c r="L10" s="11" t="s">
         <v>86</v>
       </c>
-      <c r="M10" s="12" t="s">
+      <c r="M10" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="N10" s="10" t="s">
+      <c r="N10" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="O10" s="12" t="s">
+      <c r="O10" s="13" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="10"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="10" t="s">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B11" s="11"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="8" t="s">
+      <c r="G11" s="14"/>
+      <c r="H11" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="I11" s="17" t="s">
+      <c r="I11" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="J11" s="10" t="s">
+      <c r="J11" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="L11" s="10" t="s">
+      <c r="L11" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="M11" s="13" t="s">
+      <c r="M11" s="14" t="s">
         <v>155</v>
       </c>
-      <c r="N11" s="10" t="s">
+      <c r="N11" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="O11" s="13" t="s">
+      <c r="O11" s="14" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="10"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="10" t="s">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B12" s="11"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="E12" s="11" t="s">
+      <c r="E12" s="12" t="s">
         <v>140</v>
       </c>
-      <c r="F12" s="10" t="s">
+      <c r="F12" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G12" s="11"/>
-      <c r="H12" s="10" t="s">
+      <c r="G12" s="12"/>
+      <c r="H12" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I12" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="J12" s="10" t="s">
+      <c r="J12" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K12" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="L12" s="10" t="s">
+      <c r="L12" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="M12" s="11" t="s">
+      <c r="M12" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="N12" s="10" t="s">
+      <c r="N12" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="O12" s="11" t="s">
+      <c r="O12" s="12" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="10"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="10" t="s">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B13" s="11"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="10" t="s">
+      <c r="E13" s="13"/>
+      <c r="F13" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="12"/>
-      <c r="H13" s="10" t="s">
+      <c r="G13" s="13"/>
+      <c r="H13" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="I13" s="12"/>
-      <c r="J13" s="8" t="s">
+      <c r="I13" s="13"/>
+      <c r="J13" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="10" t="s">
+      <c r="K13" s="13"/>
+      <c r="L13" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="M13" s="12"/>
-      <c r="N13" s="10" t="s">
+      <c r="M13" s="13"/>
+      <c r="N13" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="O13" s="12"/>
-    </row>
-    <row r="14" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="10"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="10" t="s">
+      <c r="O13" s="13"/>
+    </row>
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="90.2" customHeight="true">
+      <c r="B14" s="11"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="10" t="s">
+      <c r="E14" s="14"/>
+      <c r="F14" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="10" t="s">
+      <c r="G14" s="14"/>
+      <c r="H14" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="I14" s="13"/>
-      <c r="J14" s="10" t="s">
+      <c r="I14" s="14"/>
+      <c r="J14" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="K14" s="13"/>
-      <c r="L14" s="10" t="s">
+      <c r="K14" s="14"/>
+      <c r="L14" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="M14" s="13"/>
-      <c r="N14" s="10" t="s">
+      <c r="M14" s="14"/>
+      <c r="N14" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="O14" s="13"/>
+      <c r="O14" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4030,7 +4007,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="86" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="66"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/울산 아가씨.xlsx
+++ b/sheets/민요/검수/울산 아가씨.xlsx
@@ -3522,19 +3522,19 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="9" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="9" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="8" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="8" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="9" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="8" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="8" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="9" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="8" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="8" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="9" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="8" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="8" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="9" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="8" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="8" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="9" width="6"/>
   </cols>
   <sheetData>
